--- a/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9200" yWindow="3280" windowWidth="39400" windowHeight="24940" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ValueBindings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueBindings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1000,7 +1000,7 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,36 @@
         <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2942,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>applied_pressure</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Applied pressure</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The pressure applied to the test surface at which a measured response is read - for example the 150 kPa design pressure at which the settlement under a plate or zone load test is judged. Restricts the evidence of a criterion to readings taken at that applied pressure.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
@@ -1628,7 +1657,21 @@
         <f>IF(ISNA(VLOOKUP(B4,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>applied_pressure</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:evidenceCondition</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">

--- a/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
@@ -1198,12 +1198,36 @@
         <f>IF(ISNA(VLOOKUP(B5,AssociatedElements!B$2:B2943,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="9" t="n"/>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>fines_content</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Fines content</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>The fines content of the material the evidence was taken from - the percentage of particles by dry mass finer than the 75 micron (No. 200) sieve - for example a fill containing 5 to 10 % fines. Restricts the evidence of a criterion to material whose fines content lies in the stated range.</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>mass per mass</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
@@ -1678,7 +1702,21 @@
         <f>IF(ISNA(VLOOKUP(B5,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>fines_content</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:evidenceCondition</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">

--- a/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
@@ -1234,10 +1234,36 @@
         <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="G6" s="9" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>interval_duration</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Interval duration</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>The length of the time interval over which the compared value was accumulated - for example the two minutes over which penetration is judged against a refusal limit. Restricts the evidence of a criterion to values accumulated over an interval of the stated length.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
@@ -1723,7 +1749,21 @@
         <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>interval_duration</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:evidenceCondition</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">

--- a/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
@@ -1270,7 +1270,36 @@
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Relative toe amplitude</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The height of the toe reflection of a low-strain integrity test record relative to the height of its impact peak. Restricts the evidence to records whose amplification balances the toe reflection against the impact - the condition under which the relative height of an earlier reflection approximates its reflection coefficient. Stated as a range, for example 0.5 to 2.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
@@ -1770,7 +1799,21 @@
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:evidenceCondition</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">

--- a/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/evidenceCondition.xlsx
@@ -2381,13 +2381,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D2:D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"direct,horizontal_offset,difference,reverse_difference,angular_difference,containment,sequence_between,value_at,rate,rate_per_log_cycle,within_envelope,frequency"</formula1>
+      <formula1>"direct,horizontal offset,difference,reverse difference,angular difference,containment,sequence between,value at,rate,rate per log cycle,within envelope,frequency"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"design,evidence"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"value,vertical_intersection,volume_top,volume_base"</formula1>
+      <formula1>"value,vertical intersection,volume top,volume base"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
